--- a/연구코드/aec/results/강남/linear_results.xlsx
+++ b/연구코드/aec/results/강남/linear_results.xlsx
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6299</v>
+        <v>0.6306</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0517</v>
+        <v>0.0219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9456</v>
+        <v>1.9779</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/연구코드/aec/results/강남/linear_results.xlsx
+++ b/연구코드/aec/results/강남/linear_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,32 +542,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEC: p25 (표준화)</t>
+          <t>AEC: mean (표준화)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.171</v>
+        <v>9.0488</v>
       </c>
       <c r="C4" t="n">
-        <v>9.81</v>
+        <v>7.652</v>
       </c>
       <c r="D4" t="n">
-        <v>12.5319</v>
+        <v>10.4456</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6939</v>
+        <v>0.7121</v>
       </c>
       <c r="F4" t="n">
-        <v>16.0993</v>
+        <v>12.7065</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1343</v>
+        <v>0.0881</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1338</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="5">
@@ -666,72 +666,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEC: mean (표준화)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>9.0488</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.652</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4456</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.7121</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12.7065</v>
+          <t>ManufacturerModelName (F-test)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A (범주형)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>F=2.583</t>
+        </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0881</v>
+        <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0876</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ManufacturerModelName (F-test)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N/A (범주형)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>F=2.583</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="I9" t="n">
         <v>0.0276</v>
       </c>
     </row>
@@ -746,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,19 +762,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>109.8381</v>
+        <v>109.8535</v>
       </c>
       <c r="C2" t="n">
-        <v>95.2893</v>
+        <v>95.3045</v>
       </c>
       <c r="D2" t="n">
-        <v>124.3868</v>
+        <v>124.4024</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4175</v>
+        <v>7.4176</v>
       </c>
       <c r="F2" t="n">
-        <v>14.808</v>
+        <v>14.8099</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -818,19 +787,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.6045</v>
+        <v>42.722</v>
       </c>
       <c r="C3" t="n">
-        <v>40.5318</v>
+        <v>40.6613</v>
       </c>
       <c r="D3" t="n">
-        <v>44.6772</v>
+        <v>44.7826</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0567</v>
+        <v>1.0506</v>
       </c>
       <c r="F3" t="n">
-        <v>40.3175</v>
+        <v>40.6644</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -843,19 +812,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.6246</v>
+        <v>-6.6056</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.5751</v>
+        <v>-7.5554</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.6742</v>
+        <v>-5.6558</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4846</v>
+        <v>0.4842</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.6707</v>
+        <v>-13.641</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -864,26 +833,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9566</v>
+        <v>9.2879</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.562</v>
+        <v>8.103199999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>11.4753</v>
+        <v>10.4726</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8333</v>
+        <v>0.604</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0322</v>
+        <v>15.377</v>
       </c>
       <c r="G5" t="n">
-        <v>0.302144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +862,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8659</v>
+        <v>-1.5131</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.5758</v>
+        <v>-2.701</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8441</v>
+        <v>-0.3252</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8718</v>
+        <v>0.6056</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9932</v>
+        <v>-2.4983</v>
       </c>
       <c r="G6" t="n">
-        <v>0.320754</v>
+        <v>0.012576</v>
       </c>
     </row>
     <row r="7">
@@ -918,22 +887,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.371</v>
+        <v>-1.7919</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.7261</v>
+        <v>-2.8858</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0159</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6909</v>
+        <v>0.5577</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9844</v>
+        <v>-3.2133</v>
       </c>
       <c r="G7" t="n">
-        <v>0.047382</v>
+        <v>0.001338</v>
       </c>
     </row>
     <row r="8">
@@ -943,19 +912,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.8868</v>
+        <v>-5.0111</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.3105</v>
+        <v>-6.4151</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4632</v>
+        <v>-3.6072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7258</v>
+        <v>0.7158</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.7328</v>
+        <v>-7.001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -964,776 +933,751 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7831</v>
+        <v>-0.4081</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9815</v>
+        <v>-38.7723</v>
       </c>
       <c r="D9" t="n">
-        <v>12.5477</v>
+        <v>37.9561</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4488</v>
+        <v>19.5594</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6768</v>
+        <v>-0.0209</v>
       </c>
       <c r="G9" t="n">
-        <v>0.093765</v>
+        <v>0.983357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3467</v>
+        <v>13.0104</v>
       </c>
       <c r="C10" t="n">
-        <v>-38.0436</v>
+        <v>-8.4316</v>
       </c>
       <c r="D10" t="n">
-        <v>38.7369</v>
+        <v>34.4525</v>
       </c>
       <c r="E10" t="n">
-        <v>19.5727</v>
+        <v>10.932</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0177</v>
+        <v>1.1901</v>
       </c>
       <c r="G10" t="n">
-        <v>0.985872</v>
+        <v>0.234168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_BrightSpeed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.1192</v>
+        <v>21.1331</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.323499999999999</v>
+        <v>-17.1159</v>
       </c>
       <c r="D11" t="n">
-        <v>34.5619</v>
+        <v>59.3822</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9322</v>
+        <v>19.5007</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.0837</v>
       </c>
       <c r="G11" t="n">
-        <v>0.230296</v>
+        <v>0.278654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed</t>
+          <t>Model_BrightSpeed S</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.6752</v>
+        <v>-15.2163</v>
       </c>
       <c r="C12" t="n">
-        <v>-17.583</v>
+        <v>-53.845</v>
       </c>
       <c r="D12" t="n">
-        <v>58.9334</v>
+        <v>23.4124</v>
       </c>
       <c r="E12" t="n">
-        <v>19.5054</v>
+        <v>19.6943</v>
       </c>
       <c r="F12" t="n">
-        <v>1.06</v>
+        <v>-0.7726</v>
       </c>
       <c r="G12" t="n">
-        <v>0.289313</v>
+        <v>0.439856</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed S</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-14.2956</v>
+        <v>-18.0713</v>
       </c>
       <c r="C13" t="n">
-        <v>-52.9631</v>
+        <v>-38.5663</v>
       </c>
       <c r="D13" t="n">
-        <v>24.372</v>
+        <v>2.4237</v>
       </c>
       <c r="E13" t="n">
-        <v>19.7141</v>
+        <v>10.4491</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7251</v>
+        <v>-1.7295</v>
       </c>
       <c r="G13" t="n">
-        <v>0.468468</v>
+        <v>0.083915</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-17.9422</v>
+        <v>5.7423</v>
       </c>
       <c r="C14" t="n">
-        <v>-38.4383</v>
+        <v>-23.1798</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5538</v>
+        <v>34.6644</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4496</v>
+        <v>14.7455</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.717</v>
+        <v>0.3894</v>
       </c>
       <c r="G14" t="n">
-        <v>0.086164</v>
+        <v>0.697012</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.0069</v>
+        <v>6.4739</v>
       </c>
       <c r="C15" t="n">
-        <v>-22.919</v>
+        <v>-18.5854</v>
       </c>
       <c r="D15" t="n">
-        <v>34.9328</v>
+        <v>31.5331</v>
       </c>
       <c r="E15" t="n">
-        <v>14.7475</v>
+        <v>12.7761</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4073</v>
+        <v>0.5067</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683828</v>
+        <v>0.612422</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.656</v>
+        <v>-1.4934</v>
       </c>
       <c r="C16" t="n">
-        <v>-18.4052</v>
+        <v>-39.8175</v>
       </c>
       <c r="D16" t="n">
-        <v>31.7172</v>
+        <v>36.8307</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7771</v>
+        <v>19.539</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5209</v>
+        <v>-0.0764</v>
       </c>
       <c r="G16" t="n">
-        <v>0.602485</v>
+        <v>0.939086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 6</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.9792999999999999</v>
+        <v>21.8503</v>
       </c>
       <c r="C17" t="n">
-        <v>-39.3151</v>
+        <v>-3.2432</v>
       </c>
       <c r="D17" t="n">
-        <v>37.3565</v>
+        <v>46.9439</v>
       </c>
       <c r="E17" t="n">
-        <v>19.545</v>
+        <v>12.7936</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0501</v>
+        <v>1.7079</v>
       </c>
       <c r="G17" t="n">
-        <v>0.960044</v>
+        <v>0.087843</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Emotion 6</t>
+          <t>Model_IQon - Spectral CT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.9454</v>
+        <v>-3.848</v>
       </c>
       <c r="C18" t="n">
-        <v>-3.1483</v>
+        <v>-28.8872</v>
       </c>
       <c r="D18" t="n">
-        <v>47.0391</v>
+        <v>21.1913</v>
       </c>
       <c r="E18" t="n">
-        <v>12.7937</v>
+        <v>12.7659</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7153</v>
+        <v>-0.3014</v>
       </c>
       <c r="G18" t="n">
-        <v>0.086474</v>
+        <v>0.763128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_IQon - Spectral CT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-3.8755</v>
+        <v>24.9638</v>
       </c>
       <c r="C19" t="n">
-        <v>-28.9144</v>
+        <v>3.4265</v>
       </c>
       <c r="D19" t="n">
-        <v>21.1633</v>
+        <v>46.5012</v>
       </c>
       <c r="E19" t="n">
-        <v>12.7657</v>
+        <v>10.9805</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3036</v>
+        <v>2.2735</v>
       </c>
       <c r="G19" t="n">
-        <v>0.761478</v>
+        <v>0.023127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.7315</v>
+        <v>-0.6213</v>
       </c>
       <c r="C20" t="n">
-        <v>3.19</v>
+        <v>-15.28</v>
       </c>
       <c r="D20" t="n">
-        <v>46.2729</v>
+        <v>14.0374</v>
       </c>
       <c r="E20" t="n">
-        <v>10.9826</v>
+        <v>7.4735</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2519</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.024462</v>
+        <v>0.933754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.458</v>
+        <v>1.635</v>
       </c>
       <c r="C21" t="n">
-        <v>-15.1197</v>
+        <v>-17.5442</v>
       </c>
       <c r="D21" t="n">
-        <v>14.2036</v>
+        <v>20.8143</v>
       </c>
       <c r="E21" t="n">
-        <v>7.475</v>
+        <v>9.7783</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0613</v>
+        <v>0.1672</v>
       </c>
       <c r="G21" t="n">
-        <v>0.951147</v>
+        <v>0.8672260000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_LightSpeed16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8774</v>
+        <v>34.644</v>
       </c>
       <c r="C22" t="n">
-        <v>-17.307</v>
+        <v>-3.6487</v>
       </c>
       <c r="D22" t="n">
-        <v>21.0618</v>
+        <v>72.9367</v>
       </c>
       <c r="E22" t="n">
-        <v>9.780900000000001</v>
+        <v>19.523</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1919</v>
+        <v>1.7745</v>
       </c>
       <c r="G22" t="n">
-        <v>0.847808</v>
+        <v>0.07616299999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34.1999</v>
+        <v>-9.7592</v>
       </c>
       <c r="C23" t="n">
-        <v>-4.1014</v>
+        <v>-38.6871</v>
       </c>
       <c r="D23" t="n">
-        <v>72.5012</v>
+        <v>19.1687</v>
       </c>
       <c r="E23" t="n">
-        <v>19.5274</v>
+        <v>14.7485</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7514</v>
+        <v>-0.6617</v>
       </c>
       <c r="G23" t="n">
-        <v>0.080067</v>
+        <v>0.508251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-9.2258</v>
+        <v>-4.7012</v>
       </c>
       <c r="C24" t="n">
-        <v>-38.1708</v>
+        <v>-19.3874</v>
       </c>
       <c r="D24" t="n">
-        <v>19.7193</v>
+        <v>9.984999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>14.7572</v>
+        <v>7.4876</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6252</v>
+        <v>-0.6279</v>
       </c>
       <c r="G24" t="n">
-        <v>0.531946</v>
+        <v>0.530176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-4.5656</v>
+        <v>-32.0325</v>
       </c>
       <c r="C25" t="n">
-        <v>-19.2538</v>
+        <v>-70.2697</v>
       </c>
       <c r="D25" t="n">
-        <v>10.1226</v>
+        <v>6.2048</v>
       </c>
       <c r="E25" t="n">
-        <v>7.4886</v>
+        <v>19.4947</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6097</v>
+        <v>-1.6431</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5421589999999999</v>
+        <v>0.100547</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-32.1274</v>
+        <v>-20.2723</v>
       </c>
       <c r="C26" t="n">
-        <v>-70.3643</v>
+        <v>-49.4182</v>
       </c>
       <c r="D26" t="n">
-        <v>6.1095</v>
+        <v>8.8735</v>
       </c>
       <c r="E26" t="n">
-        <v>19.4945</v>
+        <v>14.8596</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.648</v>
+        <v>-1.3643</v>
       </c>
       <c r="G26" t="n">
-        <v>0.099541</v>
+        <v>0.172674</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-20.74</v>
+        <v>13.5623</v>
       </c>
       <c r="C27" t="n">
-        <v>-49.8988</v>
+        <v>-6.2062</v>
       </c>
       <c r="D27" t="n">
-        <v>8.418900000000001</v>
+        <v>33.3309</v>
       </c>
       <c r="E27" t="n">
-        <v>14.8662</v>
+        <v>10.0787</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3951</v>
+        <v>1.3456</v>
       </c>
       <c r="G27" t="n">
-        <v>0.163173</v>
+        <v>0.178605</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.8929</v>
+        <v>-4.769</v>
       </c>
       <c r="C28" t="n">
-        <v>-6.9162</v>
+        <v>-19.4169</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7019</v>
+        <v>9.8789</v>
       </c>
       <c r="E28" t="n">
-        <v>10.0994</v>
+        <v>7.468</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2766</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.201925</v>
+        <v>0.523182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.6833</v>
+        <v>3.2231</v>
       </c>
       <c r="C29" t="n">
-        <v>-19.3318</v>
+        <v>-17.267</v>
       </c>
       <c r="D29" t="n">
-        <v>9.965199999999999</v>
+        <v>23.7132</v>
       </c>
       <c r="E29" t="n">
-        <v>7.4684</v>
+        <v>10.4466</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6271</v>
+        <v>0.3085</v>
       </c>
       <c r="G29" t="n">
-        <v>0.53069</v>
+        <v>0.757718</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.752</v>
+        <v>1.4824</v>
       </c>
       <c r="C30" t="n">
-        <v>-17.7572</v>
+        <v>-15.6612</v>
       </c>
       <c r="D30" t="n">
-        <v>23.2613</v>
+        <v>18.6259</v>
       </c>
       <c r="E30" t="n">
-        <v>10.4564</v>
+        <v>8.740399999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2632</v>
+        <v>0.1696</v>
       </c>
       <c r="G30" t="n">
-        <v>0.792436</v>
+        <v>0.8653459999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4436</v>
+        <v>-2.2018</v>
       </c>
       <c r="C31" t="n">
-        <v>-15.6998</v>
+        <v>-27.382</v>
       </c>
       <c r="D31" t="n">
-        <v>18.5869</v>
+        <v>22.9784</v>
       </c>
       <c r="E31" t="n">
-        <v>8.7403</v>
+        <v>12.8378</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1652</v>
+        <v>-0.1715</v>
       </c>
       <c r="G31" t="n">
-        <v>0.868837</v>
+        <v>0.8638439999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.3188</v>
+        <v>4.8922</v>
       </c>
       <c r="C32" t="n">
-        <v>-27.4995</v>
+        <v>-24.0475</v>
       </c>
       <c r="D32" t="n">
-        <v>22.8619</v>
+        <v>33.8319</v>
       </c>
       <c r="E32" t="n">
-        <v>12.838</v>
+        <v>14.7545</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1806</v>
+        <v>0.3316</v>
       </c>
       <c r="G32" t="n">
-        <v>0.856689</v>
+        <v>0.740253</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.7078</v>
+        <v>8.1273</v>
       </c>
       <c r="C33" t="n">
-        <v>-24.2334</v>
+        <v>-30.1373</v>
       </c>
       <c r="D33" t="n">
-        <v>33.6491</v>
+        <v>46.3918</v>
       </c>
       <c r="E33" t="n">
-        <v>14.7553</v>
+        <v>19.5086</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3191</v>
+        <v>0.4166</v>
       </c>
       <c r="G33" t="n">
-        <v>0.749721</v>
+        <v>0.677027</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7.9868</v>
+        <v>24.5578</v>
       </c>
       <c r="C34" t="n">
-        <v>-30.2779</v>
+        <v>-13.692</v>
       </c>
       <c r="D34" t="n">
-        <v>46.2515</v>
+        <v>62.8076</v>
       </c>
       <c r="E34" t="n">
-        <v>19.5087</v>
+        <v>19.5011</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4094</v>
+        <v>1.2593</v>
       </c>
       <c r="G34" t="n">
-        <v>0.682303</v>
+        <v>0.208101</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.3266</v>
+        <v>43.1432</v>
       </c>
       <c r="C35" t="n">
-        <v>-13.925</v>
+        <v>14.2068</v>
       </c>
       <c r="D35" t="n">
-        <v>62.5781</v>
+        <v>72.0795</v>
       </c>
       <c r="E35" t="n">
-        <v>19.502</v>
+        <v>14.7528</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2474</v>
+        <v>2.9244</v>
       </c>
       <c r="G35" t="n">
-        <v>0.212434</v>
+        <v>0.003499</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>43.2313</v>
+        <v>-7.1985</v>
       </c>
       <c r="C36" t="n">
-        <v>14.295</v>
+        <v>-21.843</v>
       </c>
       <c r="D36" t="n">
-        <v>72.1675</v>
+        <v>7.4459</v>
       </c>
       <c r="E36" t="n">
-        <v>14.7527</v>
+        <v>7.4663</v>
       </c>
       <c r="F36" t="n">
-        <v>2.9304</v>
+        <v>-0.9641</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003432</v>
+        <v>0.335119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_iCT 128</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-7.2323</v>
+        <v>-48.6667</v>
       </c>
       <c r="C37" t="n">
-        <v>-21.8767</v>
+        <v>-87.00239999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>7.412</v>
+        <v>-10.331</v>
       </c>
       <c r="E37" t="n">
-        <v>7.4662</v>
+        <v>19.5449</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9687</v>
+        <v>-2.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.332851</v>
+        <v>0.012873</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_iCT 128</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-48.3258</v>
+        <v>19.7407</v>
       </c>
       <c r="C38" t="n">
-        <v>-86.66630000000001</v>
+        <v>-0.0266</v>
       </c>
       <c r="D38" t="n">
-        <v>-9.9854</v>
+        <v>39.508</v>
       </c>
       <c r="E38" t="n">
-        <v>19.5473</v>
+        <v>10.0781</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.4722</v>
+        <v>1.9588</v>
       </c>
       <c r="G38" t="n">
-        <v>0.013528</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Model_iCT 256</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>19.8802</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.1115</v>
-      </c>
-      <c r="D39" t="n">
-        <v>39.6489</v>
-      </c>
-      <c r="E39" t="n">
-        <v>10.0788</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.9725</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.048724</v>
+        <v>0.050309</v>
       </c>
     </row>
   </sheetData>
@@ -1785,7 +1729,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6579</v>
+        <v>0.6577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1815,7 +1759,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84.9935</v>
+        <v>87.3214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1845,7 +1789,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14463.11</v>
+        <v>14462.2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1860,7 +1804,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14669.16</v>
+        <v>14662.83</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1875,7 +1819,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.8295</v>
+        <v>17.8353</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1890,7 +1834,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.196</v>
+        <v>13.2112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1905,7 +1849,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6306</v>
+        <v>0.6311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1920,7 +1864,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0219</v>
+        <v>0.0214</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,7 +1890,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,7 +1905,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9593</v>
+        <v>0.9596</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2004,7 +1948,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>123.4141</v>
+        <v>122.8969</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2047,7 +1991,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9779</v>
+        <v>1.9769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2075,7 +2019,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>164.57</v>
+        <v>139.85</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
